--- a/Data/IceStation3d/26aug2025coring/20250826-PS149_47-1-SI_corer_9cm-019-SYI-RHO.xlsx
+++ b/Data/IceStation3d/26aug2025coring/20250826-PS149_47-1-SI_corer_9cm-019-SYI-RHO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\evsalg001\Documents\MATLAB\Contrasts coring\Data\IceStation3d\26aug2025coring\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A538E6F9-EB45-4E75-AD23-26E342C458D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71CBB5A7-6041-48BA-AF2E-9504F1CB841C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="20985" tabRatio="726" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="20985" tabRatio="726" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="metadata-core" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
     <sheet name="CT" sheetId="12" r:id="rId12"/>
     <sheet name="lists" sheetId="13" r:id="rId13"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="767" uniqueCount="377">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="763" uniqueCount="373">
   <si>
     <t>Core</t>
   </si>
@@ -1166,18 +1166,6 @@
     <t xml:space="preserve">clear ice with some small bubbles </t>
   </si>
   <si>
-    <t>C17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">part of leaked brine collected from the core craddle/cutting table of the bandsaw. </t>
-  </si>
-  <si>
-    <t>Escaped brine weight</t>
-  </si>
-  <si>
-    <t>fraction of weight escaped</t>
-  </si>
-  <si>
     <t>rho_parafine=0.8335</t>
   </si>
   <si>
@@ -1777,6 +1765,18 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1786,22 +1786,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1810,7 +1795,7 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1819,17 +1804,20 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -24129,14 +24117,14 @@
       <c r="G1" s="58" t="s">
         <v>91</v>
       </c>
-      <c r="H1" s="157" t="s">
+      <c r="H1" s="156" t="s">
         <v>92</v>
       </c>
-      <c r="I1" s="157"/>
-      <c r="J1" s="157" t="s">
+      <c r="I1" s="156"/>
+      <c r="J1" s="156" t="s">
         <v>93</v>
       </c>
-      <c r="K1" s="157"/>
+      <c r="K1" s="156"/>
       <c r="L1" s="60"/>
       <c r="M1" s="58" t="s">
         <v>95</v>
@@ -24147,10 +24135,10 @@
       </c>
       <c r="P1" s="19"/>
       <c r="Q1" s="9"/>
-      <c r="R1" s="161" t="s">
+      <c r="R1" s="159" t="s">
         <v>122</v>
       </c>
-      <c r="S1" s="161"/>
+      <c r="S1" s="159"/>
       <c r="T1" s="9"/>
       <c r="U1" s="58" t="s">
         <v>85</v>
@@ -28505,11 +28493,11 @@
         <v>20</v>
       </c>
       <c r="B3" s="24"/>
-      <c r="C3" s="149" t="s">
+      <c r="C3" s="145" t="s">
         <v>297</v>
       </c>
-      <c r="D3" s="149"/>
-      <c r="E3" s="149"/>
+      <c r="D3" s="145"/>
+      <c r="E3" s="145"/>
       <c r="F3" s="4"/>
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
@@ -28536,11 +28524,11 @@
         <v>21</v>
       </c>
       <c r="B4" s="26"/>
-      <c r="C4" s="150" t="s">
+      <c r="C4" s="146" t="s">
         <v>303</v>
       </c>
-      <c r="D4" s="150"/>
-      <c r="E4" s="150"/>
+      <c r="D4" s="146"/>
+      <c r="E4" s="146"/>
       <c r="F4" s="4"/>
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
@@ -28594,11 +28582,11 @@
     <row r="6" spans="1:25" ht="13.5" customHeight="1">
       <c r="A6" s="4"/>
       <c r="B6" s="4"/>
-      <c r="C6" s="151" t="s">
+      <c r="C6" s="147" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="151"/>
-      <c r="E6" s="151"/>
+      <c r="D6" s="147"/>
+      <c r="E6" s="147"/>
       <c r="F6" s="144" t="s">
         <v>24</v>
       </c>
@@ -29501,11 +29489,11 @@
         <v>67</v>
       </c>
       <c r="B33" s="53"/>
-      <c r="C33" s="145"/>
-      <c r="D33" s="145"/>
-      <c r="E33" s="145"/>
-      <c r="F33" s="145"/>
-      <c r="G33" s="145"/>
+      <c r="C33" s="149"/>
+      <c r="D33" s="149"/>
+      <c r="E33" s="149"/>
+      <c r="F33" s="149"/>
+      <c r="G33" s="149"/>
       <c r="H33" s="22"/>
       <c r="I33" s="22"/>
       <c r="J33" s="22"/>
@@ -29747,11 +29735,11 @@
       <c r="Y40" s="22"/>
     </row>
     <row r="41" spans="1:25">
-      <c r="A41" s="146" t="s">
+      <c r="A41" s="150" t="s">
         <v>79</v>
       </c>
-      <c r="B41" s="146"/>
-      <c r="C41" s="146"/>
+      <c r="B41" s="150"/>
+      <c r="C41" s="150"/>
       <c r="D41" s="22"/>
       <c r="E41" s="22"/>
       <c r="F41" s="22"/>
@@ -29776,14 +29764,14 @@
       <c r="Y41" s="22"/>
     </row>
     <row r="42" spans="1:25" ht="63.75" customHeight="1">
-      <c r="A42" s="147" t="s">
+      <c r="A42" s="151" t="s">
         <v>317</v>
       </c>
-      <c r="B42" s="147"/>
-      <c r="C42" s="147"/>
-      <c r="D42" s="147"/>
-      <c r="E42" s="147"/>
-      <c r="F42" s="147"/>
+      <c r="B42" s="151"/>
+      <c r="C42" s="151"/>
+      <c r="D42" s="151"/>
+      <c r="E42" s="151"/>
+      <c r="F42" s="151"/>
       <c r="G42" s="22"/>
       <c r="H42" s="22"/>
       <c r="I42" s="22"/>
@@ -30076,21 +30064,21 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A29:E29"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="A35:E35"/>
+    <mergeCell ref="A41:C41"/>
+    <mergeCell ref="A42:F42"/>
+    <mergeCell ref="F6:H6"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="F10:I10"/>
+    <mergeCell ref="A15:E15"/>
+    <mergeCell ref="A24:E24"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="C3:E3"/>
     <mergeCell ref="C4:E4"/>
     <mergeCell ref="A5:E5"/>
     <mergeCell ref="C6:E6"/>
-    <mergeCell ref="F6:H6"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="F10:I10"/>
-    <mergeCell ref="A15:E15"/>
-    <mergeCell ref="A24:E24"/>
-    <mergeCell ref="A29:E29"/>
-    <mergeCell ref="C33:G33"/>
-    <mergeCell ref="A35:E35"/>
-    <mergeCell ref="A41:C41"/>
-    <mergeCell ref="A42:F42"/>
   </mergeCells>
   <dataValidations count="6">
     <dataValidation type="date" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="date" prompt="Date in international format: YYYY-MM-DD" sqref="C12:D12" xr:uid="{00000000-0002-0000-0100-000000000000}">
@@ -31667,15 +31655,7 @@
     <row r="39" spans="1:28">
       <c r="A39" s="62"/>
       <c r="C39" s="141"/>
-      <c r="D39" s="6" t="s">
-        <v>371</v>
-      </c>
-      <c r="E39" s="62">
-        <v>4.5</v>
-      </c>
-      <c r="N39" s="6" t="s">
-        <v>372</v>
-      </c>
+      <c r="E39" s="62"/>
       <c r="O39" s="9"/>
       <c r="P39" s="9"/>
       <c r="Q39" s="9"/>
@@ -31694,13 +31674,7 @@
     <row r="40" spans="1:28">
       <c r="A40" s="62"/>
       <c r="E40" s="62"/>
-      <c r="N40" s="6" t="s">
-        <v>373</v>
-      </c>
-      <c r="O40" s="9">
-        <f>0.131-0.069</f>
-        <v>6.2E-2</v>
-      </c>
+      <c r="O40" s="9"/>
       <c r="P40" s="9"/>
       <c r="Q40" s="9"/>
       <c r="R40" s="9"/>
@@ -31718,13 +31692,7 @@
     <row r="41" spans="1:28">
       <c r="A41" s="62"/>
       <c r="E41" s="62"/>
-      <c r="N41" s="6" t="s">
-        <v>374</v>
-      </c>
-      <c r="O41" s="9">
-        <f>(8105+O40*1000)/8105-1</f>
-        <v>7.6495990129550329E-3</v>
-      </c>
+      <c r="O41" s="9"/>
       <c r="P41" s="9"/>
       <c r="Q41" s="9"/>
       <c r="R41" s="9"/>
@@ -31950,11 +31918,11 @@
       <c r="B2" s="66" t="s">
         <v>103</v>
       </c>
-      <c r="C2" s="154" t="s">
+      <c r="C2" s="153" t="s">
         <v>95</v>
       </c>
-      <c r="D2" s="154"/>
-      <c r="E2" s="154"/>
+      <c r="D2" s="153"/>
+      <c r="E2" s="153"/>
       <c r="F2" s="67"/>
       <c r="G2" s="67"/>
       <c r="H2" s="67"/>
@@ -31984,11 +31952,11 @@
       <c r="B3" s="68" t="s">
         <v>101</v>
       </c>
-      <c r="C3" s="155" t="s">
+      <c r="C3" s="154" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="155"/>
-      <c r="E3" s="155"/>
+      <c r="D3" s="154"/>
+      <c r="E3" s="154"/>
       <c r="F3" s="67"/>
       <c r="G3" s="67"/>
       <c r="H3" s="67"/>
@@ -32014,9 +31982,9 @@
     <row r="4" spans="1:26" ht="15.75">
       <c r="A4" s="69"/>
       <c r="B4" s="69"/>
-      <c r="C4" s="153"/>
-      <c r="D4" s="153"/>
-      <c r="E4" s="153"/>
+      <c r="C4" s="155"/>
+      <c r="D4" s="155"/>
+      <c r="E4" s="155"/>
       <c r="F4" s="22"/>
       <c r="G4" s="22"/>
       <c r="H4" s="22"/>
@@ -32042,9 +32010,9 @@
     <row r="5" spans="1:26" ht="15.75">
       <c r="A5" s="69"/>
       <c r="B5" s="69"/>
-      <c r="C5" s="153"/>
-      <c r="D5" s="153"/>
-      <c r="E5" s="153"/>
+      <c r="C5" s="155"/>
+      <c r="D5" s="155"/>
+      <c r="E5" s="155"/>
       <c r="F5" s="22"/>
       <c r="G5" s="22"/>
       <c r="H5" s="22"/>
@@ -32070,9 +32038,9 @@
     <row r="6" spans="1:26" ht="15.75">
       <c r="A6" s="69"/>
       <c r="B6" s="69"/>
-      <c r="C6" s="153"/>
-      <c r="D6" s="153"/>
-      <c r="E6" s="153"/>
+      <c r="C6" s="155"/>
+      <c r="D6" s="155"/>
+      <c r="E6" s="155"/>
       <c r="F6" s="22"/>
       <c r="G6" s="22"/>
       <c r="H6" s="22"/>
@@ -32098,9 +32066,9 @@
     <row r="7" spans="1:26" ht="15.75">
       <c r="A7" s="69"/>
       <c r="B7" s="69"/>
-      <c r="C7" s="153"/>
-      <c r="D7" s="153"/>
-      <c r="E7" s="153"/>
+      <c r="C7" s="155"/>
+      <c r="D7" s="155"/>
+      <c r="E7" s="155"/>
       <c r="F7" s="22"/>
       <c r="G7" s="22"/>
       <c r="H7" s="22"/>
@@ -32126,9 +32094,9 @@
     <row r="8" spans="1:26" ht="15.75">
       <c r="A8" s="69"/>
       <c r="B8" s="69"/>
-      <c r="C8" s="153"/>
-      <c r="D8" s="153"/>
-      <c r="E8" s="153"/>
+      <c r="C8" s="155"/>
+      <c r="D8" s="155"/>
+      <c r="E8" s="155"/>
       <c r="F8" s="22"/>
       <c r="G8" s="22"/>
       <c r="H8" s="22"/>
@@ -32154,9 +32122,9 @@
     <row r="9" spans="1:26" ht="15.75">
       <c r="A9" s="69"/>
       <c r="B9" s="69"/>
-      <c r="C9" s="153"/>
-      <c r="D9" s="153"/>
-      <c r="E9" s="153"/>
+      <c r="C9" s="155"/>
+      <c r="D9" s="155"/>
+      <c r="E9" s="155"/>
       <c r="F9" s="22"/>
       <c r="G9" s="22"/>
       <c r="H9" s="22"/>
@@ -32182,9 +32150,9 @@
     <row r="10" spans="1:26" ht="15.75">
       <c r="A10" s="69"/>
       <c r="B10" s="69"/>
-      <c r="C10" s="153"/>
-      <c r="D10" s="153"/>
-      <c r="E10" s="153"/>
+      <c r="C10" s="155"/>
+      <c r="D10" s="155"/>
+      <c r="E10" s="155"/>
       <c r="F10" s="22"/>
       <c r="G10" s="22"/>
       <c r="H10" s="22"/>
@@ -32210,9 +32178,9 @@
     <row r="11" spans="1:26" ht="15.75">
       <c r="A11" s="69"/>
       <c r="B11" s="69"/>
-      <c r="C11" s="153"/>
-      <c r="D11" s="153"/>
-      <c r="E11" s="153"/>
+      <c r="C11" s="155"/>
+      <c r="D11" s="155"/>
+      <c r="E11" s="155"/>
       <c r="F11" s="22"/>
       <c r="G11" s="22"/>
       <c r="H11" s="22"/>
@@ -32238,9 +32206,9 @@
     <row r="12" spans="1:26" ht="15.75">
       <c r="A12" s="69"/>
       <c r="B12" s="69"/>
-      <c r="C12" s="153"/>
-      <c r="D12" s="153"/>
-      <c r="E12" s="153"/>
+      <c r="C12" s="155"/>
+      <c r="D12" s="155"/>
+      <c r="E12" s="155"/>
       <c r="F12" s="22"/>
       <c r="G12" s="22"/>
       <c r="H12" s="22"/>
@@ -32266,9 +32234,9 @@
     <row r="13" spans="1:26" ht="15.75">
       <c r="A13" s="69"/>
       <c r="B13" s="69"/>
-      <c r="C13" s="153"/>
-      <c r="D13" s="153"/>
-      <c r="E13" s="153"/>
+      <c r="C13" s="155"/>
+      <c r="D13" s="155"/>
+      <c r="E13" s="155"/>
       <c r="F13" s="22"/>
       <c r="G13" s="22"/>
       <c r="H13" s="22"/>
@@ -32294,9 +32262,9 @@
     <row r="14" spans="1:26" ht="15.75">
       <c r="A14" s="69"/>
       <c r="B14" s="69"/>
-      <c r="C14" s="153"/>
-      <c r="D14" s="153"/>
-      <c r="E14" s="153"/>
+      <c r="C14" s="155"/>
+      <c r="D14" s="155"/>
+      <c r="E14" s="155"/>
       <c r="F14" s="22"/>
       <c r="G14" s="22"/>
       <c r="H14" s="22"/>
@@ -32322,9 +32290,9 @@
     <row r="15" spans="1:26" ht="15.75">
       <c r="A15" s="69"/>
       <c r="B15" s="69"/>
-      <c r="C15" s="153"/>
-      <c r="D15" s="153"/>
-      <c r="E15" s="153"/>
+      <c r="C15" s="155"/>
+      <c r="D15" s="155"/>
+      <c r="E15" s="155"/>
       <c r="F15" s="22"/>
       <c r="G15" s="22"/>
       <c r="H15" s="22"/>
@@ -32350,9 +32318,9 @@
     <row r="16" spans="1:26" ht="15.75">
       <c r="A16" s="69"/>
       <c r="B16" s="69"/>
-      <c r="C16" s="153"/>
-      <c r="D16" s="153"/>
-      <c r="E16" s="153"/>
+      <c r="C16" s="155"/>
+      <c r="D16" s="155"/>
+      <c r="E16" s="155"/>
       <c r="F16" s="22"/>
       <c r="G16" s="22"/>
       <c r="H16" s="22"/>
@@ -32378,9 +32346,9 @@
     <row r="17" spans="1:26" ht="15.75">
       <c r="A17" s="69"/>
       <c r="B17" s="69"/>
-      <c r="C17" s="153"/>
-      <c r="D17" s="153"/>
-      <c r="E17" s="153"/>
+      <c r="C17" s="155"/>
+      <c r="D17" s="155"/>
+      <c r="E17" s="155"/>
       <c r="F17" s="22"/>
       <c r="G17" s="22"/>
       <c r="H17" s="22"/>
@@ -32406,9 +32374,9 @@
     <row r="18" spans="1:26" ht="15.75">
       <c r="A18" s="69"/>
       <c r="B18" s="69"/>
-      <c r="C18" s="153"/>
-      <c r="D18" s="153"/>
-      <c r="E18" s="153"/>
+      <c r="C18" s="155"/>
+      <c r="D18" s="155"/>
+      <c r="E18" s="155"/>
       <c r="F18" s="22"/>
       <c r="G18" s="22"/>
       <c r="H18" s="22"/>
@@ -32434,9 +32402,9 @@
     <row r="19" spans="1:26" ht="15.75">
       <c r="A19" s="69"/>
       <c r="B19" s="69"/>
-      <c r="C19" s="153"/>
-      <c r="D19" s="153"/>
-      <c r="E19" s="153"/>
+      <c r="C19" s="155"/>
+      <c r="D19" s="155"/>
+      <c r="E19" s="155"/>
       <c r="F19" s="22"/>
       <c r="G19" s="22"/>
       <c r="H19" s="22"/>
@@ -32462,9 +32430,9 @@
     <row r="20" spans="1:26" ht="15.75">
       <c r="A20" s="69"/>
       <c r="B20" s="69"/>
-      <c r="C20" s="153"/>
-      <c r="D20" s="153"/>
-      <c r="E20" s="153"/>
+      <c r="C20" s="155"/>
+      <c r="D20" s="155"/>
+      <c r="E20" s="155"/>
       <c r="F20" s="22"/>
       <c r="G20" s="22"/>
       <c r="H20" s="22"/>
@@ -32490,9 +32458,9 @@
     <row r="21" spans="1:26" ht="15.75">
       <c r="A21" s="69"/>
       <c r="B21" s="69"/>
-      <c r="C21" s="153"/>
-      <c r="D21" s="153"/>
-      <c r="E21" s="153"/>
+      <c r="C21" s="155"/>
+      <c r="D21" s="155"/>
+      <c r="E21" s="155"/>
       <c r="F21" s="22"/>
       <c r="G21" s="22"/>
       <c r="H21" s="22"/>
@@ -32518,9 +32486,9 @@
     <row r="22" spans="1:26" ht="15.75">
       <c r="A22" s="69"/>
       <c r="B22" s="69"/>
-      <c r="C22" s="153"/>
-      <c r="D22" s="153"/>
-      <c r="E22" s="153"/>
+      <c r="C22" s="155"/>
+      <c r="D22" s="155"/>
+      <c r="E22" s="155"/>
       <c r="F22" s="22"/>
       <c r="G22" s="22"/>
       <c r="H22" s="22"/>
@@ -32546,9 +32514,9 @@
     <row r="23" spans="1:26" ht="15.75">
       <c r="A23" s="69"/>
       <c r="B23" s="69"/>
-      <c r="C23" s="153"/>
-      <c r="D23" s="153"/>
-      <c r="E23" s="153"/>
+      <c r="C23" s="155"/>
+      <c r="D23" s="155"/>
+      <c r="E23" s="155"/>
       <c r="F23" s="22"/>
       <c r="G23" s="22"/>
       <c r="H23" s="22"/>
@@ -32574,9 +32542,9 @@
     <row r="24" spans="1:26" ht="15.75">
       <c r="A24" s="69"/>
       <c r="B24" s="69"/>
-      <c r="C24" s="153"/>
-      <c r="D24" s="153"/>
-      <c r="E24" s="153"/>
+      <c r="C24" s="155"/>
+      <c r="D24" s="155"/>
+      <c r="E24" s="155"/>
       <c r="F24" s="22"/>
       <c r="G24" s="22"/>
       <c r="H24" s="22"/>
@@ -32602,9 +32570,9 @@
     <row r="25" spans="1:26" ht="15.75">
       <c r="A25" s="69"/>
       <c r="B25" s="69"/>
-      <c r="C25" s="153"/>
-      <c r="D25" s="153"/>
-      <c r="E25" s="153"/>
+      <c r="C25" s="155"/>
+      <c r="D25" s="155"/>
+      <c r="E25" s="155"/>
       <c r="F25" s="22"/>
       <c r="G25" s="22"/>
       <c r="H25" s="22"/>
@@ -32630,9 +32598,9 @@
     <row r="26" spans="1:26" ht="15.75">
       <c r="A26" s="69"/>
       <c r="B26" s="69"/>
-      <c r="C26" s="153"/>
-      <c r="D26" s="153"/>
-      <c r="E26" s="153"/>
+      <c r="C26" s="155"/>
+      <c r="D26" s="155"/>
+      <c r="E26" s="155"/>
       <c r="F26" s="22"/>
       <c r="G26" s="22"/>
       <c r="H26" s="22"/>
@@ -32658,9 +32626,9 @@
     <row r="27" spans="1:26" ht="15.75">
       <c r="A27" s="69"/>
       <c r="B27" s="69"/>
-      <c r="C27" s="153"/>
-      <c r="D27" s="153"/>
-      <c r="E27" s="153"/>
+      <c r="C27" s="155"/>
+      <c r="D27" s="155"/>
+      <c r="E27" s="155"/>
       <c r="F27" s="22"/>
       <c r="G27" s="22"/>
       <c r="H27" s="22"/>
@@ -32686,9 +32654,9 @@
     <row r="28" spans="1:26" ht="15.75">
       <c r="A28" s="69"/>
       <c r="B28" s="69"/>
-      <c r="C28" s="153"/>
-      <c r="D28" s="153"/>
-      <c r="E28" s="153"/>
+      <c r="C28" s="155"/>
+      <c r="D28" s="155"/>
+      <c r="E28" s="155"/>
       <c r="F28" s="22"/>
       <c r="G28" s="22"/>
       <c r="H28" s="22"/>
@@ -32714,9 +32682,9 @@
     <row r="29" spans="1:26" ht="15.75">
       <c r="A29" s="69"/>
       <c r="B29" s="69"/>
-      <c r="C29" s="153"/>
-      <c r="D29" s="153"/>
-      <c r="E29" s="153"/>
+      <c r="C29" s="155"/>
+      <c r="D29" s="155"/>
+      <c r="E29" s="155"/>
       <c r="F29" s="22"/>
       <c r="G29" s="22"/>
       <c r="H29" s="22"/>
@@ -32742,9 +32710,9 @@
     <row r="30" spans="1:26" ht="15.75">
       <c r="A30" s="69"/>
       <c r="B30" s="69"/>
-      <c r="C30" s="153"/>
-      <c r="D30" s="153"/>
-      <c r="E30" s="153"/>
+      <c r="C30" s="155"/>
+      <c r="D30" s="155"/>
+      <c r="E30" s="155"/>
       <c r="F30" s="22"/>
       <c r="G30" s="22"/>
       <c r="H30" s="22"/>
@@ -32770,9 +32738,9 @@
     <row r="31" spans="1:26" ht="15.75">
       <c r="A31" s="69"/>
       <c r="B31" s="69"/>
-      <c r="C31" s="153"/>
-      <c r="D31" s="153"/>
-      <c r="E31" s="153"/>
+      <c r="C31" s="155"/>
+      <c r="D31" s="155"/>
+      <c r="E31" s="155"/>
       <c r="F31" s="22"/>
       <c r="G31" s="22"/>
       <c r="H31" s="22"/>
@@ -32798,9 +32766,9 @@
     <row r="32" spans="1:26" ht="15.75">
       <c r="A32" s="69"/>
       <c r="B32" s="69"/>
-      <c r="C32" s="153"/>
-      <c r="D32" s="153"/>
-      <c r="E32" s="153"/>
+      <c r="C32" s="155"/>
+      <c r="D32" s="155"/>
+      <c r="E32" s="155"/>
       <c r="F32" s="22"/>
       <c r="G32" s="22"/>
       <c r="H32" s="22"/>
@@ -32826,9 +32794,9 @@
     <row r="33" spans="1:26" ht="15.75">
       <c r="A33" s="69"/>
       <c r="B33" s="69"/>
-      <c r="C33" s="153"/>
-      <c r="D33" s="153"/>
-      <c r="E33" s="153"/>
+      <c r="C33" s="155"/>
+      <c r="D33" s="155"/>
+      <c r="E33" s="155"/>
       <c r="F33" s="22"/>
       <c r="G33" s="22"/>
       <c r="H33" s="22"/>
@@ -32854,9 +32822,9 @@
     <row r="34" spans="1:26" ht="15.75">
       <c r="A34" s="69"/>
       <c r="B34" s="69"/>
-      <c r="C34" s="153"/>
-      <c r="D34" s="153"/>
-      <c r="E34" s="153"/>
+      <c r="C34" s="155"/>
+      <c r="D34" s="155"/>
+      <c r="E34" s="155"/>
       <c r="F34" s="22"/>
       <c r="G34" s="22"/>
       <c r="H34" s="22"/>
@@ -32882,9 +32850,9 @@
     <row r="35" spans="1:26" ht="15.75">
       <c r="A35" s="69"/>
       <c r="B35" s="69"/>
-      <c r="C35" s="153"/>
-      <c r="D35" s="153"/>
-      <c r="E35" s="153"/>
+      <c r="C35" s="155"/>
+      <c r="D35" s="155"/>
+      <c r="E35" s="155"/>
       <c r="F35" s="22"/>
       <c r="G35" s="22"/>
       <c r="H35" s="22"/>
@@ -32910,9 +32878,9 @@
     <row r="36" spans="1:26" ht="15.75">
       <c r="A36" s="69"/>
       <c r="B36" s="69"/>
-      <c r="C36" s="153"/>
-      <c r="D36" s="153"/>
-      <c r="E36" s="153"/>
+      <c r="C36" s="155"/>
+      <c r="D36" s="155"/>
+      <c r="E36" s="155"/>
       <c r="F36" s="22"/>
       <c r="G36" s="22"/>
       <c r="H36" s="22"/>
@@ -32938,9 +32906,9 @@
     <row r="37" spans="1:26" ht="15.75">
       <c r="A37" s="69"/>
       <c r="B37" s="69"/>
-      <c r="C37" s="153"/>
-      <c r="D37" s="153"/>
-      <c r="E37" s="153"/>
+      <c r="C37" s="155"/>
+      <c r="D37" s="155"/>
+      <c r="E37" s="155"/>
       <c r="F37" s="22"/>
       <c r="G37" s="22"/>
       <c r="H37" s="22"/>
@@ -32966,9 +32934,9 @@
     <row r="38" spans="1:26" ht="15.75">
       <c r="A38" s="69"/>
       <c r="B38" s="69"/>
-      <c r="C38" s="153"/>
-      <c r="D38" s="153"/>
-      <c r="E38" s="153"/>
+      <c r="C38" s="155"/>
+      <c r="D38" s="155"/>
+      <c r="E38" s="155"/>
       <c r="F38" s="22"/>
       <c r="G38" s="22"/>
       <c r="H38" s="22"/>
@@ -32994,9 +32962,9 @@
     <row r="39" spans="1:26" ht="15.75">
       <c r="A39" s="69"/>
       <c r="B39" s="69"/>
-      <c r="C39" s="153"/>
-      <c r="D39" s="153"/>
-      <c r="E39" s="153"/>
+      <c r="C39" s="155"/>
+      <c r="D39" s="155"/>
+      <c r="E39" s="155"/>
       <c r="F39" s="22"/>
       <c r="G39" s="22"/>
       <c r="H39" s="22"/>
@@ -33049,36 +33017,6 @@
     </row>
   </sheetData>
   <mergeCells count="38">
-    <mergeCell ref="C2:E2"/>
-    <mergeCell ref="C3:E3"/>
-    <mergeCell ref="C4:E4"/>
-    <mergeCell ref="C5:E5"/>
-    <mergeCell ref="C6:E6"/>
-    <mergeCell ref="C7:E7"/>
-    <mergeCell ref="C8:E8"/>
-    <mergeCell ref="C9:E9"/>
-    <mergeCell ref="C10:E10"/>
-    <mergeCell ref="C11:E11"/>
-    <mergeCell ref="C12:E12"/>
-    <mergeCell ref="C13:E13"/>
-    <mergeCell ref="C14:E14"/>
-    <mergeCell ref="C15:E15"/>
-    <mergeCell ref="C16:E16"/>
-    <mergeCell ref="C17:E17"/>
-    <mergeCell ref="C18:E18"/>
-    <mergeCell ref="C19:E19"/>
-    <mergeCell ref="C20:E20"/>
-    <mergeCell ref="C21:E21"/>
-    <mergeCell ref="C22:E22"/>
-    <mergeCell ref="C23:E23"/>
-    <mergeCell ref="C24:E24"/>
-    <mergeCell ref="C25:E25"/>
-    <mergeCell ref="C26:E26"/>
-    <mergeCell ref="C27:E27"/>
-    <mergeCell ref="C28:E28"/>
-    <mergeCell ref="C29:E29"/>
-    <mergeCell ref="C30:E30"/>
-    <mergeCell ref="C31:E31"/>
     <mergeCell ref="C37:E37"/>
     <mergeCell ref="C38:E38"/>
     <mergeCell ref="C39:E39"/>
@@ -33087,6 +33025,36 @@
     <mergeCell ref="C34:E34"/>
     <mergeCell ref="C35:E35"/>
     <mergeCell ref="C36:E36"/>
+    <mergeCell ref="C27:E27"/>
+    <mergeCell ref="C28:E28"/>
+    <mergeCell ref="C29:E29"/>
+    <mergeCell ref="C30:E30"/>
+    <mergeCell ref="C31:E31"/>
+    <mergeCell ref="C22:E22"/>
+    <mergeCell ref="C23:E23"/>
+    <mergeCell ref="C24:E24"/>
+    <mergeCell ref="C25:E25"/>
+    <mergeCell ref="C26:E26"/>
+    <mergeCell ref="C17:E17"/>
+    <mergeCell ref="C18:E18"/>
+    <mergeCell ref="C19:E19"/>
+    <mergeCell ref="C20:E20"/>
+    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="C12:E12"/>
+    <mergeCell ref="C13:E13"/>
+    <mergeCell ref="C14:E14"/>
+    <mergeCell ref="C15:E15"/>
+    <mergeCell ref="C16:E16"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="C9:E9"/>
+    <mergeCell ref="C10:E10"/>
+    <mergeCell ref="C11:E11"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="C4:E4"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="C6:E6"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C1" xr:uid="{00000000-0002-0000-0300-000000000000}">
@@ -33168,10 +33136,10 @@
       <c r="C2" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="D2" s="157" t="s">
+      <c r="D2" s="156" t="s">
         <v>105</v>
       </c>
-      <c r="E2" s="157"/>
+      <c r="E2" s="156"/>
       <c r="F2" s="1" t="s">
         <v>95</v>
       </c>
@@ -33206,10 +33174,10 @@
       <c r="C3" s="71" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="158" t="s">
+      <c r="D3" s="157" t="s">
         <v>106</v>
       </c>
-      <c r="E3" s="158"/>
+      <c r="E3" s="157"/>
       <c r="F3" s="71" t="s">
         <v>1</v>
       </c>
@@ -33241,8 +33209,8 @@
       <c r="B4" s="62">
         <v>0.89</v>
       </c>
-      <c r="D4" s="156"/>
-      <c r="E4" s="156"/>
+      <c r="D4" s="158"/>
+      <c r="E4" s="158"/>
       <c r="F4" s="6" t="s">
         <v>307</v>
       </c>
@@ -33275,8 +33243,8 @@
         <f>A5+0.7</f>
         <v>1.5899999999999999</v>
       </c>
-      <c r="D5" s="156"/>
-      <c r="E5" s="156"/>
+      <c r="D5" s="158"/>
+      <c r="E5" s="158"/>
       <c r="F5" s="6" t="s">
         <v>308</v>
       </c>
@@ -33305,10 +33273,10 @@
       <c r="C6" s="6">
         <v>0.19</v>
       </c>
-      <c r="D6" s="156" t="s">
+      <c r="D6" s="158" t="s">
         <v>181</v>
       </c>
-      <c r="E6" s="156"/>
+      <c r="E6" s="158"/>
       <c r="G6" s="9"/>
       <c r="H6" s="9"/>
       <c r="I6" s="9"/>
@@ -33334,10 +33302,10 @@
       <c r="C7">
         <v>0.56999999999999995</v>
       </c>
-      <c r="D7" s="156" t="s">
+      <c r="D7" s="158" t="s">
         <v>181</v>
       </c>
-      <c r="E7" s="156"/>
+      <c r="E7" s="158"/>
       <c r="F7"/>
       <c r="G7" s="9"/>
       <c r="H7" s="9"/>
@@ -33362,8 +33330,8 @@
     </row>
     <row r="8" spans="1:26">
       <c r="A8" s="62"/>
-      <c r="D8" s="156"/>
-      <c r="E8" s="156"/>
+      <c r="D8" s="158"/>
+      <c r="E8" s="158"/>
       <c r="G8" s="9"/>
       <c r="H8" s="9"/>
       <c r="I8" s="9"/>
@@ -33387,8 +33355,8 @@
     </row>
     <row r="9" spans="1:26">
       <c r="A9" s="62"/>
-      <c r="D9" s="156"/>
-      <c r="E9" s="156"/>
+      <c r="D9" s="158"/>
+      <c r="E9" s="158"/>
       <c r="G9" s="9"/>
       <c r="H9" s="9"/>
       <c r="I9" s="9"/>
@@ -33412,8 +33380,8 @@
     </row>
     <row r="10" spans="1:26">
       <c r="A10" s="62"/>
-      <c r="D10" s="156"/>
-      <c r="E10" s="156"/>
+      <c r="D10" s="158"/>
+      <c r="E10" s="158"/>
       <c r="G10" s="9"/>
       <c r="H10" s="9"/>
       <c r="I10" s="9"/>
@@ -33437,8 +33405,8 @@
     </row>
     <row r="11" spans="1:26">
       <c r="A11" s="62"/>
-      <c r="D11" s="156"/>
-      <c r="E11" s="156"/>
+      <c r="D11" s="158"/>
+      <c r="E11" s="158"/>
       <c r="G11" s="9"/>
       <c r="H11" s="9"/>
       <c r="I11" s="9"/>
@@ -33462,8 +33430,8 @@
     </row>
     <row r="12" spans="1:26">
       <c r="A12" s="62"/>
-      <c r="D12" s="156"/>
-      <c r="E12" s="156"/>
+      <c r="D12" s="158"/>
+      <c r="E12" s="158"/>
       <c r="G12" s="9"/>
       <c r="H12" s="9"/>
       <c r="I12" s="9"/>
@@ -33487,8 +33455,8 @@
     </row>
     <row r="13" spans="1:26">
       <c r="A13" s="62"/>
-      <c r="D13" s="156"/>
-      <c r="E13" s="156"/>
+      <c r="D13" s="158"/>
+      <c r="E13" s="158"/>
       <c r="G13" s="9"/>
       <c r="H13" s="9"/>
       <c r="I13" s="9"/>
@@ -33512,8 +33480,8 @@
     </row>
     <row r="14" spans="1:26">
       <c r="A14" s="62"/>
-      <c r="D14" s="156"/>
-      <c r="E14" s="156"/>
+      <c r="D14" s="158"/>
+      <c r="E14" s="158"/>
       <c r="G14" s="9"/>
       <c r="H14" s="9"/>
       <c r="I14" s="9"/>
@@ -33537,8 +33505,8 @@
     </row>
     <row r="15" spans="1:26">
       <c r="A15" s="62"/>
-      <c r="D15" s="156"/>
-      <c r="E15" s="156"/>
+      <c r="D15" s="158"/>
+      <c r="E15" s="158"/>
       <c r="G15" s="9"/>
       <c r="H15" s="9"/>
       <c r="I15" s="9"/>
@@ -33562,8 +33530,8 @@
     </row>
     <row r="16" spans="1:26">
       <c r="A16" s="62"/>
-      <c r="D16" s="156"/>
-      <c r="E16" s="156"/>
+      <c r="D16" s="158"/>
+      <c r="E16" s="158"/>
       <c r="G16" s="9"/>
       <c r="H16" s="9"/>
       <c r="I16" s="9"/>
@@ -33587,8 +33555,8 @@
     </row>
     <row r="17" spans="1:26">
       <c r="A17" s="62"/>
-      <c r="D17" s="156"/>
-      <c r="E17" s="156"/>
+      <c r="D17" s="158"/>
+      <c r="E17" s="158"/>
       <c r="G17" s="9"/>
       <c r="H17" s="9"/>
       <c r="I17" s="9"/>
@@ -33612,8 +33580,8 @@
     </row>
     <row r="18" spans="1:26">
       <c r="A18" s="62"/>
-      <c r="D18" s="156"/>
-      <c r="E18" s="156"/>
+      <c r="D18" s="158"/>
+      <c r="E18" s="158"/>
       <c r="G18" s="9"/>
       <c r="H18" s="9"/>
       <c r="I18" s="9"/>
@@ -33637,8 +33605,8 @@
     </row>
     <row r="19" spans="1:26">
       <c r="A19" s="62"/>
-      <c r="D19" s="156"/>
-      <c r="E19" s="156"/>
+      <c r="D19" s="158"/>
+      <c r="E19" s="158"/>
       <c r="G19" s="9"/>
       <c r="H19" s="9"/>
       <c r="I19" s="9"/>
@@ -33662,8 +33630,8 @@
     </row>
     <row r="20" spans="1:26">
       <c r="A20" s="62"/>
-      <c r="D20" s="156"/>
-      <c r="E20" s="156"/>
+      <c r="D20" s="158"/>
+      <c r="E20" s="158"/>
       <c r="G20" s="9"/>
       <c r="H20" s="9"/>
       <c r="I20" s="9"/>
@@ -33687,8 +33655,8 @@
     </row>
     <row r="21" spans="1:26">
       <c r="A21" s="62"/>
-      <c r="D21" s="156"/>
-      <c r="E21" s="156"/>
+      <c r="D21" s="158"/>
+      <c r="E21" s="158"/>
       <c r="G21" s="9"/>
       <c r="H21" s="9"/>
       <c r="I21" s="9"/>
@@ -33712,8 +33680,8 @@
     </row>
     <row r="22" spans="1:26">
       <c r="A22" s="62"/>
-      <c r="D22" s="156"/>
-      <c r="E22" s="156"/>
+      <c r="D22" s="158"/>
+      <c r="E22" s="158"/>
       <c r="G22" s="9"/>
       <c r="H22" s="9"/>
       <c r="I22" s="9"/>
@@ -33737,8 +33705,8 @@
     </row>
     <row r="23" spans="1:26">
       <c r="A23" s="62"/>
-      <c r="D23" s="156"/>
-      <c r="E23" s="156"/>
+      <c r="D23" s="158"/>
+      <c r="E23" s="158"/>
       <c r="G23" s="9"/>
       <c r="H23" s="9"/>
       <c r="I23" s="9"/>
@@ -33763,8 +33731,8 @@
     <row r="24" spans="1:26">
       <c r="A24" s="62"/>
       <c r="B24" s="62"/>
-      <c r="D24" s="156"/>
-      <c r="E24" s="156"/>
+      <c r="D24" s="158"/>
+      <c r="E24" s="158"/>
       <c r="G24" s="9"/>
       <c r="H24" s="9"/>
       <c r="I24" s="9"/>
@@ -33788,8 +33756,8 @@
     </row>
     <row r="25" spans="1:26">
       <c r="A25" s="62"/>
-      <c r="D25" s="156"/>
-      <c r="E25" s="156"/>
+      <c r="D25" s="158"/>
+      <c r="E25" s="158"/>
       <c r="G25" s="9"/>
       <c r="H25" s="9"/>
       <c r="I25" s="9"/>
@@ -33815,8 +33783,8 @@
       <c r="A26" s="62"/>
       <c r="B26" s="59"/>
       <c r="C26" s="59"/>
-      <c r="D26" s="156"/>
-      <c r="E26" s="156"/>
+      <c r="D26" s="158"/>
+      <c r="E26" s="158"/>
       <c r="F26" s="59"/>
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
@@ -33843,8 +33811,8 @@
       <c r="A27" s="62"/>
       <c r="B27" s="59"/>
       <c r="C27" s="59"/>
-      <c r="D27" s="156"/>
-      <c r="E27" s="156"/>
+      <c r="D27" s="158"/>
+      <c r="E27" s="158"/>
       <c r="F27" s="59"/>
       <c r="G27" s="2"/>
       <c r="H27" s="2"/>
@@ -33869,8 +33837,8 @@
     </row>
     <row r="28" spans="1:26">
       <c r="A28" s="62"/>
-      <c r="D28" s="156"/>
-      <c r="E28" s="156"/>
+      <c r="D28" s="158"/>
+      <c r="E28" s="158"/>
       <c r="G28" s="9"/>
       <c r="H28" s="9"/>
       <c r="I28" s="9"/>
@@ -33894,8 +33862,8 @@
     </row>
     <row r="29" spans="1:26">
       <c r="A29" s="62"/>
-      <c r="D29" s="156"/>
-      <c r="E29" s="156"/>
+      <c r="D29" s="158"/>
+      <c r="E29" s="158"/>
       <c r="G29" s="9"/>
       <c r="H29" s="9"/>
       <c r="I29" s="9"/>
@@ -33919,8 +33887,8 @@
     </row>
     <row r="30" spans="1:26">
       <c r="A30" s="62"/>
-      <c r="D30" s="156"/>
-      <c r="E30" s="156"/>
+      <c r="D30" s="158"/>
+      <c r="E30" s="158"/>
       <c r="G30" s="9"/>
       <c r="H30" s="9"/>
       <c r="I30" s="9"/>
@@ -33944,8 +33912,8 @@
     </row>
     <row r="31" spans="1:26">
       <c r="A31" s="62"/>
-      <c r="D31" s="156"/>
-      <c r="E31" s="156"/>
+      <c r="D31" s="158"/>
+      <c r="E31" s="158"/>
       <c r="G31" s="9"/>
       <c r="H31" s="9"/>
       <c r="I31" s="9"/>
@@ -33969,8 +33937,8 @@
     </row>
     <row r="32" spans="1:26">
       <c r="A32" s="62"/>
-      <c r="D32" s="156"/>
-      <c r="E32" s="156"/>
+      <c r="D32" s="158"/>
+      <c r="E32" s="158"/>
       <c r="G32" s="9"/>
       <c r="H32" s="9"/>
       <c r="I32" s="9"/>
@@ -33994,8 +33962,8 @@
     </row>
     <row r="33" spans="1:26">
       <c r="A33" s="62"/>
-      <c r="D33" s="156"/>
-      <c r="E33" s="156"/>
+      <c r="D33" s="158"/>
+      <c r="E33" s="158"/>
       <c r="G33" s="9"/>
       <c r="H33" s="9"/>
       <c r="I33" s="9"/>
@@ -34019,8 +33987,8 @@
     </row>
     <row r="34" spans="1:26">
       <c r="A34" s="62"/>
-      <c r="D34" s="156"/>
-      <c r="E34" s="156"/>
+      <c r="D34" s="158"/>
+      <c r="E34" s="158"/>
       <c r="G34" s="9"/>
       <c r="H34" s="9"/>
       <c r="I34" s="9"/>
@@ -34044,8 +34012,8 @@
     </row>
     <row r="35" spans="1:26">
       <c r="A35" s="62"/>
-      <c r="D35" s="156"/>
-      <c r="E35" s="156"/>
+      <c r="D35" s="158"/>
+      <c r="E35" s="158"/>
       <c r="G35" s="9"/>
       <c r="H35" s="9"/>
       <c r="I35" s="9"/>
@@ -34069,8 +34037,8 @@
     </row>
     <row r="36" spans="1:26">
       <c r="A36" s="62"/>
-      <c r="D36" s="156"/>
-      <c r="E36" s="156"/>
+      <c r="D36" s="158"/>
+      <c r="E36" s="158"/>
       <c r="G36" s="9"/>
       <c r="H36" s="9"/>
       <c r="I36" s="9"/>
@@ -34094,8 +34062,8 @@
     </row>
     <row r="37" spans="1:26">
       <c r="A37" s="62"/>
-      <c r="D37" s="156"/>
-      <c r="E37" s="156"/>
+      <c r="D37" s="158"/>
+      <c r="E37" s="158"/>
       <c r="G37" s="9"/>
       <c r="H37" s="9"/>
       <c r="I37" s="9"/>
@@ -34119,8 +34087,8 @@
     </row>
     <row r="38" spans="1:26">
       <c r="A38" s="62"/>
-      <c r="D38" s="156"/>
-      <c r="E38" s="156"/>
+      <c r="D38" s="158"/>
+      <c r="E38" s="158"/>
       <c r="G38" s="9"/>
       <c r="H38" s="9"/>
       <c r="I38" s="9"/>
@@ -34144,8 +34112,8 @@
     </row>
     <row r="39" spans="1:26">
       <c r="A39" s="62"/>
-      <c r="D39" s="156"/>
-      <c r="E39" s="156"/>
+      <c r="D39" s="158"/>
+      <c r="E39" s="158"/>
       <c r="G39" s="9"/>
       <c r="H39" s="9"/>
       <c r="I39" s="9"/>
@@ -34169,8 +34137,8 @@
     </row>
     <row r="40" spans="1:26">
       <c r="A40" s="62"/>
-      <c r="D40" s="156"/>
-      <c r="E40" s="156"/>
+      <c r="D40" s="158"/>
+      <c r="E40" s="158"/>
       <c r="G40" s="9"/>
       <c r="H40" s="9"/>
       <c r="I40" s="9"/>
@@ -34194,8 +34162,8 @@
     </row>
     <row r="41" spans="1:26">
       <c r="A41" s="62"/>
-      <c r="D41" s="156"/>
-      <c r="E41" s="156"/>
+      <c r="D41" s="158"/>
+      <c r="E41" s="158"/>
       <c r="G41" s="9"/>
       <c r="H41" s="9"/>
       <c r="I41" s="9"/>
@@ -34219,8 +34187,8 @@
     </row>
     <row r="42" spans="1:26">
       <c r="A42" s="62"/>
-      <c r="D42" s="156"/>
-      <c r="E42" s="156"/>
+      <c r="D42" s="158"/>
+      <c r="E42" s="158"/>
       <c r="G42" s="9"/>
       <c r="H42" s="9"/>
       <c r="I42" s="9"/>
@@ -34244,8 +34212,8 @@
     </row>
     <row r="43" spans="1:26">
       <c r="A43" s="62"/>
-      <c r="D43" s="156"/>
-      <c r="E43" s="156"/>
+      <c r="D43" s="158"/>
+      <c r="E43" s="158"/>
       <c r="G43" s="9"/>
       <c r="H43" s="9"/>
       <c r="I43" s="9"/>
@@ -34269,8 +34237,8 @@
     </row>
     <row r="44" spans="1:26">
       <c r="A44" s="62"/>
-      <c r="D44" s="156"/>
-      <c r="E44" s="156"/>
+      <c r="D44" s="158"/>
+      <c r="E44" s="158"/>
       <c r="G44" s="9"/>
       <c r="H44" s="9"/>
       <c r="I44" s="9"/>
@@ -34294,8 +34262,8 @@
     </row>
     <row r="45" spans="1:26">
       <c r="A45" s="62"/>
-      <c r="D45" s="156"/>
-      <c r="E45" s="156"/>
+      <c r="D45" s="158"/>
+      <c r="E45" s="158"/>
       <c r="G45" s="9"/>
       <c r="H45" s="9"/>
       <c r="I45" s="9"/>
@@ -34319,8 +34287,8 @@
     </row>
     <row r="46" spans="1:26">
       <c r="A46" s="62"/>
-      <c r="D46" s="156"/>
-      <c r="E46" s="156"/>
+      <c r="D46" s="158"/>
+      <c r="E46" s="158"/>
       <c r="G46" s="9"/>
       <c r="H46" s="9"/>
       <c r="I46" s="9"/>
@@ -34372,52 +34340,52 @@
     </row>
   </sheetData>
   <mergeCells count="46">
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="D35:E35"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="D37:E37"/>
-    <mergeCell ref="D38:E38"/>
-    <mergeCell ref="D39:E39"/>
-    <mergeCell ref="D40:E40"/>
-    <mergeCell ref="D41:E41"/>
     <mergeCell ref="D47:E47"/>
     <mergeCell ref="D42:E42"/>
     <mergeCell ref="D43:E43"/>
     <mergeCell ref="D44:E44"/>
     <mergeCell ref="D45:E45"/>
     <mergeCell ref="D46:E46"/>
+    <mergeCell ref="D37:E37"/>
+    <mergeCell ref="D38:E38"/>
+    <mergeCell ref="D39:E39"/>
+    <mergeCell ref="D40:E40"/>
+    <mergeCell ref="D41:E41"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="D6:E6"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C1" xr:uid="{00000000-0002-0000-0400-000000000000}">
@@ -36931,7 +36899,7 @@
       <c r="A37" s="62"/>
       <c r="D37" s="62"/>
       <c r="H37" s="6" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="I37" s="9"/>
       <c r="J37" s="9"/>
@@ -36952,7 +36920,7 @@
       <c r="A38" s="62"/>
       <c r="D38" s="62"/>
       <c r="H38" s="6" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="I38" s="9"/>
       <c r="J38" s="9"/>
@@ -37211,58 +37179,58 @@
       <c r="E2" s="58" t="s">
         <v>121</v>
       </c>
-      <c r="F2" s="161" t="s">
+      <c r="F2" s="159" t="s">
         <v>122</v>
       </c>
-      <c r="G2" s="161"/>
-      <c r="H2" s="161" t="s">
+      <c r="G2" s="159"/>
+      <c r="H2" s="159" t="s">
         <v>123</v>
       </c>
-      <c r="I2" s="161"/>
-      <c r="J2" s="162" t="s">
+      <c r="I2" s="159"/>
+      <c r="J2" s="160" t="s">
         <v>124</v>
       </c>
-      <c r="K2" s="162"/>
-      <c r="L2" s="161" t="s">
+      <c r="K2" s="160"/>
+      <c r="L2" s="159" t="s">
         <v>125</v>
       </c>
-      <c r="M2" s="161"/>
-      <c r="N2" s="162" t="s">
+      <c r="M2" s="159"/>
+      <c r="N2" s="160" t="s">
         <v>126</v>
       </c>
-      <c r="O2" s="162"/>
-      <c r="P2" s="160" t="s">
+      <c r="O2" s="160"/>
+      <c r="P2" s="162" t="s">
         <v>127</v>
       </c>
-      <c r="Q2" s="160"/>
-      <c r="R2" s="157" t="s">
+      <c r="Q2" s="162"/>
+      <c r="R2" s="156" t="s">
         <v>128</v>
       </c>
-      <c r="S2" s="157"/>
-      <c r="T2" s="160" t="s">
+      <c r="S2" s="156"/>
+      <c r="T2" s="162" t="s">
         <v>129</v>
       </c>
-      <c r="U2" s="160"/>
-      <c r="V2" s="157" t="s">
+      <c r="U2" s="162"/>
+      <c r="V2" s="156" t="s">
         <v>130</v>
       </c>
-      <c r="W2" s="157"/>
-      <c r="X2" s="160" t="s">
+      <c r="W2" s="156"/>
+      <c r="X2" s="162" t="s">
         <v>131</v>
       </c>
-      <c r="Y2" s="160"/>
-      <c r="Z2" s="159" t="s">
+      <c r="Y2" s="162"/>
+      <c r="Z2" s="161" t="s">
         <v>132</v>
       </c>
-      <c r="AA2" s="159"/>
-      <c r="AB2" s="159" t="s">
+      <c r="AA2" s="161"/>
+      <c r="AB2" s="161" t="s">
         <v>133</v>
       </c>
-      <c r="AC2" s="159"/>
-      <c r="AD2" s="160" t="s">
+      <c r="AC2" s="161"/>
+      <c r="AD2" s="162" t="s">
         <v>134</v>
       </c>
-      <c r="AE2" s="160"/>
+      <c r="AE2" s="162"/>
       <c r="AF2" s="58" t="s">
         <v>95</v>
       </c>
@@ -38633,11 +38601,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="L2:M2"/>
-    <mergeCell ref="N2:O2"/>
     <mergeCell ref="Z2:AA2"/>
     <mergeCell ref="AB2:AC2"/>
     <mergeCell ref="AD2:AE2"/>
@@ -38646,6 +38609,11 @@
     <mergeCell ref="T2:U2"/>
     <mergeCell ref="V2:W2"/>
     <mergeCell ref="X2:Y2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="N2:O2"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C1" xr:uid="{00000000-0002-0000-0700-000000000000}">
